--- a/Big_Data/Taller_2/Resultados2.xlsx
+++ b/Big_Data/Taller_2/Resultados2.xlsx
@@ -358,502 +358,502 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2">
-        <v>9.387986577749494</v>
+        <v>9.797939020440598</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3">
-        <v>8.819327677977213</v>
+        <v>13.85778241506941</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4">
-        <v>14.72559756258032</v>
+        <v>13.43719750677221</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5">
-        <v>11.4000937830722</v>
+        <v>9.597717455282986</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6">
-        <v>13.70580084274305</v>
+        <v>9.924767171328448</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7">
-        <v>13.69790184549217</v>
+        <v>11.79192029230418</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8">
-        <v>11.90249624483022</v>
+        <v>8.718234549831745</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9">
-        <v>14.10129013310623</v>
+        <v>13.27577988331979</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10">
-        <v>9.593515962128674</v>
+        <v>9.583948356457817</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11">
-        <v>10.95798417334461</v>
+        <v>13.73020230324681</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12">
-        <v>12.23387716491227</v>
+        <v>9.110366297679095</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13">
-        <v>8.006007622711131</v>
+        <v>10.59853865260592</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14">
-        <v>10.17012107053491</v>
+        <v>8.547821363968652</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15">
-        <v>10.4421591699193</v>
+        <v>11.74468979474698</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16">
-        <v>9.560834504400587</v>
+        <v>12.41589473851898</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17">
-        <v>11.73158687141067</v>
+        <v>13.68834274347964</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18">
-        <v>11.31642911385616</v>
+        <v>13.10962561303317</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19">
-        <v>13.35945133107765</v>
+        <v>13.83040414363477</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>12.81843583257328</v>
+        <v>14.93799176765413</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>14.22674168887547</v>
+        <v>14.79274654413479</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>8.186340206885191</v>
+        <v>11.82816327761764</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23">
-        <v>12.96118741915729</v>
+        <v>10.43658031800624</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24">
-        <v>11.02665969981976</v>
+        <v>14.01584398158281</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25">
-        <v>11.57910185812608</v>
+        <v>8.069461934649455</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>10.21035750972513</v>
+        <v>9.667838933887833</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>10.2369319162668</v>
+        <v>9.789743426810045</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>13.84420780057773</v>
+        <v>12.52185397000173</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29">
-        <v>9.404860363345733</v>
+        <v>14.71372373750983</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30">
-        <v>9.661079297181477</v>
+        <v>13.77537710125365</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31">
-        <v>12.6400673100547</v>
+        <v>8.294950586989115</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32">
-        <v>14.06237897084982</v>
+        <v>12.17998934150151</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33">
-        <v>12.51897438019664</v>
+        <v>14.12499865661743</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34">
-        <v>8.921071381809142</v>
+        <v>13.82760454129147</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35">
-        <v>14.1523986743612</v>
+        <v>14.33129590395055</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36">
-        <v>12.24980422011739</v>
+        <v>11.41137143662882</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37">
-        <v>9.113203059849498</v>
+        <v>12.48707263160538</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>12.60091333264052</v>
+        <v>11.07171779171624</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>8.827746994221057</v>
+        <v>9.952342941372184</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>9.111515321032986</v>
+        <v>11.49926624204505</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41">
-        <v>11.0064345205415</v>
+        <v>9.937961212221801</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42">
-        <v>12.37223719499796</v>
+        <v>14.81211420163507</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43">
-        <v>13.66569955829086</v>
+        <v>12.96722437482039</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44">
-        <v>11.47556131693417</v>
+        <v>11.88077000288414</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45">
-        <v>11.96502003381042</v>
+        <v>13.43981672434792</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46">
-        <v>13.53232837390536</v>
+        <v>14.27744394670471</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47">
-        <v>11.21077580810809</v>
+        <v>13.15429185546261</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48">
-        <v>11.79086109558926</v>
+        <v>11.40519034786173</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49">
-        <v>12.15619499234283</v>
+        <v>9.777944281793758</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50">
-        <v>14.24450255116406</v>
+        <v>8.150197182788364</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51">
-        <v>12.63829463100057</v>
+        <v>12.72336330521318</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52">
-        <v>12.77336326071458</v>
+        <v>8.794697084758054</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53">
-        <v>12.54631840032755</v>
+        <v>8.284162744838701</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54">
-        <v>13.1303708551405</v>
+        <v>9.742002268071619</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55">
-        <v>14.60606418418259</v>
+        <v>13.92953092594272</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56">
-        <v>8.48033072854518</v>
+        <v>9.921954930960077</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57">
-        <v>12.7367991215656</v>
+        <v>8.155283568733942</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58">
-        <v>11.04639078589157</v>
+        <v>11.18898700955381</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59">
-        <v>11.65418511578436</v>
+        <v>13.09971534459926</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60">
-        <v>9.51217410377965</v>
+        <v>12.05619810866003</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61">
-        <v>8.444234397801473</v>
+        <v>11.35419835785233</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62">
-        <v>10.58047450850044</v>
+        <v>9.995976513495615</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63">
-        <v>9.779656184691264</v>
+        <v>10.48457572948423</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64">
-        <v>8.807238353979619</v>
+        <v>8.889522200841416</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65">
-        <v>12.88830956665959</v>
+        <v>9.53949808249854</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66">
-        <v>9.784867746861561</v>
+        <v>11.11753696264696</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67">
-        <v>8.114710823588693</v>
+        <v>10.85612551484526</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68">
-        <v>12.76087627210284</v>
+        <v>13.05319989199144</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69">
-        <v>8.807056762271559</v>
+        <v>13.9815446665465</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70">
-        <v>9.774354761678291</v>
+        <v>12.70662381876759</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71">
-        <v>12.30608965521659</v>
+        <v>12.6942390898589</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72">
-        <v>13.25151433726189</v>
+        <v>12.17052885431396</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73">
-        <v>10.92122305636318</v>
+        <v>8.838003040944614</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>8.91394312729183</v>
+        <v>12.93122843173457</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>14.09619649595371</v>
+        <v>9.29097214084593</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>10.58304601658464</v>
+        <v>10.30628639269269</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77">
-        <v>11.3078948862761</v>
+        <v>10.69533178357814</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78">
-        <v>9.543108004425036</v>
+        <v>14.35679331331288</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79">
-        <v>8.987632622434901</v>
+        <v>8.810007735936503</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80">
-        <v>13.02664423317046</v>
+        <v>10.77448243555276</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81">
-        <v>9.346547482272516</v>
+        <v>14.8160196074112</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82">
-        <v>12.98530509969314</v>
+        <v>8.114394413202469</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83">
-        <v>13.19520817493754</v>
+        <v>8.381444723958777</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84">
-        <v>13.89368983211819</v>
+        <v>11.52358835283914</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85">
-        <v>13.08296583262043</v>
+        <v>8.753339404242842</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86">
-        <v>14.55467127008537</v>
+        <v>14.90253692272067</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87">
-        <v>13.63945741091055</v>
+        <v>11.13931969228857</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88">
-        <v>11.73967823323099</v>
+        <v>13.70769562081872</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89">
-        <v>8.150359357709288</v>
+        <v>10.88894232342351</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90">
-        <v>13.09059608467397</v>
+        <v>14.83299171998922</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91">
-        <v>14.44112645925068</v>
+        <v>12.18682436835718</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92">
-        <v>9.404105275207746</v>
+        <v>8.876669077807614</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93">
-        <v>14.60972036320914</v>
+        <v>8.996651436280089</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94">
-        <v>13.31417135067449</v>
+        <v>11.92303460125225</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95">
-        <v>8.21592446554712</v>
+        <v>12.16649096402534</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96">
-        <v>9.934075634492935</v>
+        <v>9.3175832858661</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97">
-        <v>13.22102107233388</v>
+        <v>8.601220079085158</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98">
-        <v>12.66964928841731</v>
+        <v>14.06519377899415</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99">
-        <v>12.53740574968578</v>
+        <v>13.01560939917615</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100">
-        <v>12.73062892951651</v>
+        <v>9.151489885526082</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101">
-        <v>12.78214432432615</v>
+        <v>9.990421741041237</v>
       </c>
     </row>
   </sheetData>

--- a/Big_Data/Taller_2/Resultados2.xlsx
+++ b/Big_Data/Taller_2/Resultados2.xlsx
@@ -358,502 +358,502 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2">
-        <v>9.797939020440598</v>
+        <v>12.9738081864439</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3">
-        <v>13.85778241506941</v>
+        <v>8.709246676220099</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4">
-        <v>13.43719750677221</v>
+        <v>14.26524853541391</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5">
-        <v>9.597717455282986</v>
+        <v>14.73025803291035</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6">
-        <v>9.924767171328448</v>
+        <v>9.212322683798218</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7">
-        <v>11.79192029230418</v>
+        <v>12.88530762996876</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8">
-        <v>8.718234549831745</v>
+        <v>12.76863058674187</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9">
-        <v>13.27577988331979</v>
+        <v>13.39648210883734</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10">
-        <v>9.583948356457817</v>
+        <v>13.56881864109378</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11">
-        <v>13.73020230324681</v>
+        <v>8.322474711835731</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12">
-        <v>9.110366297679095</v>
+        <v>13.08983409897774</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13">
-        <v>10.59853865260592</v>
+        <v>8.954818263908058</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14">
-        <v>8.547821363968652</v>
+        <v>11.33026119028405</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15">
-        <v>11.74468979474698</v>
+        <v>11.38862649149989</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16">
-        <v>12.41589473851898</v>
+        <v>13.99795386320045</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17">
-        <v>13.68834274347964</v>
+        <v>14.48648945062352</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18">
-        <v>13.10962561303317</v>
+        <v>11.63644127254056</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19">
-        <v>13.83040414363477</v>
+        <v>8.150629114492743</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>14.93799176765413</v>
+        <v>13.06299886867527</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>14.79274654413479</v>
+        <v>14.47356136897744</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>11.82816327761764</v>
+        <v>9.30477619451254</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23">
-        <v>10.43658031800624</v>
+        <v>8.960149133569978</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24">
-        <v>14.01584398158281</v>
+        <v>13.55471297526962</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25">
-        <v>8.069461934649455</v>
+        <v>14.66289232816985</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>9.667838933887833</v>
+        <v>12.49456861995717</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>9.789743426810045</v>
+        <v>11.97901866926638</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>12.52185397000173</v>
+        <v>13.78932377260299</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29">
-        <v>14.71372373750983</v>
+        <v>13.68385288047827</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30">
-        <v>13.77537710125365</v>
+        <v>9.474691736947753</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31">
-        <v>8.294950586989115</v>
+        <v>11.74992178195468</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32">
-        <v>12.17998934150151</v>
+        <v>13.39312277352187</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33">
-        <v>14.12499865661743</v>
+        <v>12.67107677149824</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34">
-        <v>13.82760454129147</v>
+        <v>10.81897166713435</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35">
-        <v>14.33129590395055</v>
+        <v>10.67652440254025</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36">
-        <v>11.41137143662882</v>
+        <v>9.634923922733719</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37">
-        <v>12.48707263160538</v>
+        <v>8.34737296865379</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>11.07171779171624</v>
+        <v>8.174736045903272</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>9.952342941372184</v>
+        <v>10.69436496788884</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>11.49926624204505</v>
+        <v>8.845139111955795</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41">
-        <v>9.937961212221801</v>
+        <v>10.90658370962</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42">
-        <v>14.81211420163507</v>
+        <v>9.438746368358968</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43">
-        <v>12.96722437482039</v>
+        <v>12.10552932360313</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44">
-        <v>11.88077000288414</v>
+        <v>12.19826181004677</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45">
-        <v>13.43981672434792</v>
+        <v>12.63528274877531</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46">
-        <v>14.27744394670471</v>
+        <v>14.30557963333009</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47">
-        <v>13.15429185546261</v>
+        <v>14.98021784222597</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48">
-        <v>11.40519034786173</v>
+        <v>11.78614679482887</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49">
-        <v>9.777944281793758</v>
+        <v>8.062494984257148</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50">
-        <v>8.150197182788364</v>
+        <v>9.696374030115626</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51">
-        <v>12.72336330521318</v>
+        <v>11.26219873170498</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52">
-        <v>8.794697084758054</v>
+        <v>8.443605520048568</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53">
-        <v>8.284162744838701</v>
+        <v>11.33372948022393</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54">
-        <v>9.742002268071619</v>
+        <v>12.74552042985393</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55">
-        <v>13.92953092594272</v>
+        <v>9.924235821166807</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56">
-        <v>9.921954930960077</v>
+        <v>10.71674926905991</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57">
-        <v>8.155283568733942</v>
+        <v>8.09904471798847</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58">
-        <v>11.18898700955381</v>
+        <v>13.9897411680471</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59">
-        <v>13.09971534459926</v>
+        <v>8.942757663307235</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60">
-        <v>12.05619810866003</v>
+        <v>12.56980608407793</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61">
-        <v>11.35419835785233</v>
+        <v>9.365375284382965</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62">
-        <v>9.995976513495615</v>
+        <v>12.6432410007213</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63">
-        <v>10.48457572948423</v>
+        <v>9.083581534015439</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64">
-        <v>8.889522200841416</v>
+        <v>11.75796966008128</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65">
-        <v>9.53949808249854</v>
+        <v>14.82116579591439</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66">
-        <v>11.11753696264696</v>
+        <v>13.37049533065631</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67">
-        <v>10.85612551484526</v>
+        <v>10.87432518032047</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68">
-        <v>13.05319989199144</v>
+        <v>10.96837614338196</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69">
-        <v>13.9815446665465</v>
+        <v>9.564199834564562</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70">
-        <v>12.70662381876759</v>
+        <v>8.342786300467296</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71">
-        <v>12.6942390898589</v>
+        <v>11.72807617832284</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72">
-        <v>12.17052885431396</v>
+        <v>14.31315085737207</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73">
-        <v>8.838003040944614</v>
+        <v>13.15651636153134</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>12.93122843173457</v>
+        <v>13.60840319915497</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>9.29097214084593</v>
+        <v>10.92448867308462</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>10.30628639269269</v>
+        <v>13.16300385136382</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77">
-        <v>10.69533178357814</v>
+        <v>8.284275101764713</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78">
-        <v>14.35679331331288</v>
+        <v>14.47340519024827</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79">
-        <v>8.810007735936503</v>
+        <v>9.500643419500456</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80">
-        <v>10.77448243555276</v>
+        <v>14.75853994161988</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81">
-        <v>14.8160196074112</v>
+        <v>9.623645171091638</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82">
-        <v>8.114394413202469</v>
+        <v>14.34213367478716</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83">
-        <v>8.381444723958777</v>
+        <v>8.311896652235125</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84">
-        <v>11.52358835283914</v>
+        <v>11.54045084390164</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85">
-        <v>8.753339404242842</v>
+        <v>12.05939544574392</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86">
-        <v>14.90253692272067</v>
+        <v>13.14120706916353</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87">
-        <v>11.13931969228857</v>
+        <v>8.355336333449788</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88">
-        <v>13.70769562081872</v>
+        <v>9.52060514522131</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89">
-        <v>10.88894232342351</v>
+        <v>8.085290516352645</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90">
-        <v>14.83299171998922</v>
+        <v>8.574871134115323</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91">
-        <v>12.18682436835718</v>
+        <v>9.810689972021112</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92">
-        <v>8.876669077807614</v>
+        <v>11.81114800453741</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93">
-        <v>8.996651436280089</v>
+        <v>10.52589627380618</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94">
-        <v>11.92303460125225</v>
+        <v>10.68795269111257</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95">
-        <v>12.16649096402534</v>
+        <v>10.76674860704767</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96">
-        <v>9.3175832858661</v>
+        <v>9.109485150862842</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97">
-        <v>8.601220079085158</v>
+        <v>12.77450243414478</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98">
-        <v>14.06519377899415</v>
+        <v>12.10311584971001</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99">
-        <v>13.01560939917615</v>
+        <v>13.56632499104432</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100">
-        <v>9.151489885526082</v>
+        <v>10.90895878696258</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101">
-        <v>9.990421741041237</v>
+        <v>11.74108674508635</v>
       </c>
     </row>
   </sheetData>

--- a/Big_Data/Taller_2/Resultados2.xlsx
+++ b/Big_Data/Taller_2/Resultados2.xlsx
@@ -23,8 +23,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -40,7 +48,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +56,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -352,508 +378,508 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2">
-        <v>12.9738081864439</v>
+        <v>13.17084385990719</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3">
-        <v>8.709246676220099</v>
+        <v>13.20022650765147</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4">
-        <v>14.26524853541391</v>
+        <v>14.16590624330023</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5">
-        <v>14.73025803291035</v>
+        <v>14.87763743220594</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6">
-        <v>9.212322683798218</v>
+        <v>9.539324160072081</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7">
-        <v>12.88530762996876</v>
+        <v>8.653037819597015</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8">
-        <v>12.76863058674187</v>
+        <v>9.020090611345791</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9">
-        <v>13.39648210883734</v>
+        <v>10.87599895332344</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10">
-        <v>13.56881864109378</v>
+        <v>10.50736989666386</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11">
-        <v>8.322474711835731</v>
+        <v>14.80239915370234</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12">
-        <v>13.08983409897774</v>
+        <v>12.600613238897</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13">
-        <v>8.954818263908058</v>
+        <v>12.70202079933042</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14">
-        <v>11.33026119028405</v>
+        <v>13.18054716583074</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15">
-        <v>11.38862649149989</v>
+        <v>12.45942987314165</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16">
-        <v>13.99795386320045</v>
+        <v>14.28150241768318</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17">
-        <v>14.48648945062352</v>
+        <v>10.23412921273457</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18">
-        <v>11.63644127254056</v>
+        <v>8.826844397807319</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19">
-        <v>8.150629114492743</v>
+        <v>9.609265358241732</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>13.06299886867527</v>
+        <v>8.72039761352204</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>14.47356136897744</v>
+        <v>14.80066444599595</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>9.30477619451254</v>
+        <v>11.24304566324156</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23">
-        <v>8.960149133569978</v>
+        <v>9.495339947753937</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24">
-        <v>13.55471297526962</v>
+        <v>11.17861447802369</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25">
-        <v>14.66289232816985</v>
+        <v>14.99596417193802</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>12.49456861995717</v>
+        <v>8.692573279519344</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>11.97901866926638</v>
+        <v>9.661364581942532</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>13.78932377260299</v>
+        <v>8.940426965704473</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29">
-        <v>13.68385288047827</v>
+        <v>13.07221480209972</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30">
-        <v>9.474691736947753</v>
+        <v>10.40186729431163</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31">
-        <v>11.74992178195468</v>
+        <v>8.617162072527979</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32">
-        <v>13.39312277352187</v>
+        <v>13.85183708593082</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33">
-        <v>12.67107677149824</v>
+        <v>8.833698218846799</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34">
-        <v>10.81897166713435</v>
+        <v>8.245137794230171</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35">
-        <v>10.67652440254025</v>
+        <v>9.27144333230793</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36">
-        <v>9.634923922733719</v>
+        <v>14.80891781550587</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37">
-        <v>8.34737296865379</v>
+        <v>9.491498366770722</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>8.174736045903272</v>
+        <v>11.50344856589824</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>10.69436496788884</v>
+        <v>13.88699696901968</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>8.845139111955795</v>
+        <v>11.21742324889355</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41">
-        <v>10.90658370962</v>
+        <v>13.51295700983843</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42">
-        <v>9.438746368358968</v>
+        <v>9.348683744068303</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43">
-        <v>12.10552932360313</v>
+        <v>9.43966124049285</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44">
-        <v>12.19826181004677</v>
+        <v>14.31071089766366</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45">
-        <v>12.63528274877531</v>
+        <v>12.39646309622772</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46">
-        <v>14.30557963333009</v>
+        <v>10.42470687683856</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47">
-        <v>14.98021784222597</v>
+        <v>11.23045479001934</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48">
-        <v>11.78614679482887</v>
+        <v>12.24091439576155</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49">
-        <v>8.062494984257148</v>
+        <v>9.126430519327105</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50">
-        <v>9.696374030115626</v>
+        <v>13.0809385217436</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51">
-        <v>11.26219873170498</v>
+        <v>9.119081251962488</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52">
-        <v>8.443605520048568</v>
+        <v>11.05943268126971</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53">
-        <v>11.33372948022393</v>
+        <v>10.32693279254462</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54">
-        <v>12.74552042985393</v>
+        <v>10.59499524003315</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55">
-        <v>9.924235821166807</v>
+        <v>11.8696825808669</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56">
-        <v>10.71674926905991</v>
+        <v>9.294718943806293</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57">
-        <v>8.09904471798847</v>
+        <v>10.15580286509811</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58">
-        <v>13.9897411680471</v>
+        <v>8.642308236523114</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59">
-        <v>8.942757663307235</v>
+        <v>13.43412127044715</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60">
-        <v>12.56980608407793</v>
+        <v>12.6626981291231</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61">
-        <v>9.365375284382965</v>
+        <v>10.79639931351997</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62">
-        <v>12.6432410007213</v>
+        <v>9.819307737403824</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63">
-        <v>9.083581534015439</v>
+        <v>12.39144858729671</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64">
-        <v>11.75796966008128</v>
+        <v>13.99220103337103</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65">
-        <v>14.82116579591439</v>
+        <v>11.24595585671245</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66">
-        <v>13.37049533065631</v>
+        <v>10.08588020342098</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67">
-        <v>10.87432518032047</v>
+        <v>9.091351626488649</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68">
-        <v>10.96837614338196</v>
+        <v>11.29183549754664</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69">
-        <v>9.564199834564562</v>
+        <v>9.709194604569523</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70">
-        <v>8.342786300467296</v>
+        <v>10.48368595278808</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71">
-        <v>11.72807617832284</v>
+        <v>11.38941087380941</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72">
-        <v>14.31315085737207</v>
+        <v>14.27417818758756</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73">
-        <v>13.15651636153134</v>
+        <v>9.323437475369127</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>13.60840319915497</v>
+        <v>8.812144656786829</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>10.92448867308462</v>
+        <v>9.898975085713868</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>13.16300385136382</v>
+        <v>9.028215142626408</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77">
-        <v>8.284275101764713</v>
+        <v>12.30628675928099</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78">
-        <v>14.47340519024827</v>
+        <v>14.65600854111062</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79">
-        <v>9.500643419500456</v>
+        <v>14.92915426939192</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80">
-        <v>14.75853994161988</v>
+        <v>10.39886398647979</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81">
-        <v>9.623645171091638</v>
+        <v>13.29506177224263</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82">
-        <v>14.34213367478716</v>
+        <v>9.696013265270297</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83">
-        <v>8.311896652235125</v>
+        <v>12.53484317108846</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84">
-        <v>11.54045084390164</v>
+        <v>9.742683729622506</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85">
-        <v>12.05939544574392</v>
+        <v>11.28874909043457</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86">
-        <v>13.14120706916353</v>
+        <v>12.3165336760038</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87">
-        <v>8.355336333449788</v>
+        <v>13.28793332270002</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88">
-        <v>9.52060514522131</v>
+        <v>9.283268266378677</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89">
-        <v>8.085290516352645</v>
+        <v>9.917718301625701</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90">
-        <v>8.574871134115323</v>
+        <v>10.70358665943414</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91">
-        <v>9.810689972021112</v>
+        <v>12.91270185018699</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92">
-        <v>11.81114800453741</v>
+        <v>14.86355769520079</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93">
-        <v>10.52589627380618</v>
+        <v>10.12271686040044</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94">
-        <v>10.68795269111257</v>
+        <v>13.85049310189092</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95">
-        <v>10.76674860704767</v>
+        <v>13.56669021208592</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96">
-        <v>9.109485150862842</v>
+        <v>10.92844882736538</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97">
-        <v>12.77450243414478</v>
+        <v>8.417467315451864</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98">
-        <v>12.10311584971001</v>
+        <v>10.6276119350898</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99">
-        <v>13.56632499104432</v>
+        <v>13.47510602916661</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100">
-        <v>10.90895878696258</v>
+        <v>12.46886544557196</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101">
-        <v>11.74108674508635</v>
+        <v>10.87706038295048</v>
       </c>
     </row>
   </sheetData>

--- a/Big_Data/Taller_2/Resultados2.xlsx
+++ b/Big_Data/Taller_2/Resultados2.xlsx
@@ -384,502 +384,502 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2">
-        <v>13.17084385990719</v>
+        <v>12.9738081864439</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3">
-        <v>13.20022650765147</v>
+        <v>8.709246676220099</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4">
-        <v>14.16590624330023</v>
+        <v>14.26524853541391</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5">
-        <v>14.87763743220594</v>
+        <v>14.73025803291035</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6">
-        <v>9.539324160072081</v>
+        <v>9.212322683798218</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7">
-        <v>8.653037819597015</v>
+        <v>12.88530762996876</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8">
-        <v>9.020090611345791</v>
+        <v>12.76863058674187</v>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9">
-        <v>10.87599895332344</v>
+        <v>13.39648210883734</v>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10">
-        <v>10.50736989666386</v>
+        <v>13.56881864109378</v>
       </c>
     </row>
     <row r="11" spans="1:1">
       <c r="A11">
-        <v>14.80239915370234</v>
+        <v>8.322474711835731</v>
       </c>
     </row>
     <row r="12" spans="1:1">
       <c r="A12">
-        <v>12.600613238897</v>
+        <v>13.08983409897774</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13">
-        <v>12.70202079933042</v>
+        <v>8.954818263908058</v>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14">
-        <v>13.18054716583074</v>
+        <v>11.33026119028405</v>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15">
-        <v>12.45942987314165</v>
+        <v>11.38862649149989</v>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16">
-        <v>14.28150241768318</v>
+        <v>13.99795386320045</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17">
-        <v>10.23412921273457</v>
+        <v>14.48648945062352</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18">
-        <v>8.826844397807319</v>
+        <v>11.63644127254056</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19">
-        <v>9.609265358241732</v>
+        <v>8.150629114492743</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20">
-        <v>8.72039761352204</v>
+        <v>13.06299886867527</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21">
-        <v>14.80066444599595</v>
+        <v>14.47356136897744</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22">
-        <v>11.24304566324156</v>
+        <v>9.30477619451254</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23">
-        <v>9.495339947753937</v>
+        <v>8.960149133569978</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24">
-        <v>11.17861447802369</v>
+        <v>13.55471297526962</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25">
-        <v>14.99596417193802</v>
+        <v>14.66289232816985</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26">
-        <v>8.692573279519344</v>
+        <v>12.49456861995717</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27">
-        <v>9.661364581942532</v>
+        <v>11.97901866926638</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28">
-        <v>8.940426965704473</v>
+        <v>13.78932377260299</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29">
-        <v>13.07221480209972</v>
+        <v>13.68385288047827</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30">
-        <v>10.40186729431163</v>
+        <v>9.474691736947753</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31">
-        <v>8.617162072527979</v>
+        <v>11.74992178195468</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32">
-        <v>13.85183708593082</v>
+        <v>13.39312277352187</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33">
-        <v>8.833698218846799</v>
+        <v>12.67107677149824</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34">
-        <v>8.245137794230171</v>
+        <v>10.81897166713435</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35">
-        <v>9.27144333230793</v>
+        <v>10.67652440254025</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36">
-        <v>14.80891781550587</v>
+        <v>9.634923922733719</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37">
-        <v>9.491498366770722</v>
+        <v>8.34737296865379</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38">
-        <v>11.50344856589824</v>
+        <v>8.174736045903272</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39">
-        <v>13.88699696901968</v>
+        <v>10.69436496788884</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40">
-        <v>11.21742324889355</v>
+        <v>8.845139111955795</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41">
-        <v>13.51295700983843</v>
+        <v>10.90658370962</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42">
-        <v>9.348683744068303</v>
+        <v>9.438746368358968</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43">
-        <v>9.43966124049285</v>
+        <v>12.10552932360313</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44">
-        <v>14.31071089766366</v>
+        <v>12.19826181004677</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45">
-        <v>12.39646309622772</v>
+        <v>12.63528274877531</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46">
-        <v>10.42470687683856</v>
+        <v>14.30557963333009</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47">
-        <v>11.23045479001934</v>
+        <v>14.98021784222597</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48">
-        <v>12.24091439576155</v>
+        <v>11.78614679482887</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49">
-        <v>9.126430519327105</v>
+        <v>8.062494984257148</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50">
-        <v>13.0809385217436</v>
+        <v>9.696374030115626</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51">
-        <v>9.119081251962488</v>
+        <v>11.26219873170498</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52">
-        <v>11.05943268126971</v>
+        <v>8.443605520048568</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53">
-        <v>10.32693279254462</v>
+        <v>11.33372948022393</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54">
-        <v>10.59499524003315</v>
+        <v>12.74552042985393</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55">
-        <v>11.8696825808669</v>
+        <v>9.924235821166807</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56">
-        <v>9.294718943806293</v>
+        <v>10.71674926905991</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57">
-        <v>10.15580286509811</v>
+        <v>8.09904471798847</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58">
-        <v>8.642308236523114</v>
+        <v>13.9897411680471</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59">
-        <v>13.43412127044715</v>
+        <v>8.942757663307235</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60">
-        <v>12.6626981291231</v>
+        <v>12.56980608407793</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61">
-        <v>10.79639931351997</v>
+        <v>9.365375284382965</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62">
-        <v>9.819307737403824</v>
+        <v>12.6432410007213</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63">
-        <v>12.39144858729671</v>
+        <v>9.083581534015439</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64">
-        <v>13.99220103337103</v>
+        <v>11.75796966008128</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65">
-        <v>11.24595585671245</v>
+        <v>14.82116579591439</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66">
-        <v>10.08588020342098</v>
+        <v>13.37049533065631</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67">
-        <v>9.091351626488649</v>
+        <v>10.87432518032047</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68">
-        <v>11.29183549754664</v>
+        <v>10.96837614338196</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69">
-        <v>9.709194604569523</v>
+        <v>9.564199834564562</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70">
-        <v>10.48368595278808</v>
+        <v>8.342786300467296</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71">
-        <v>11.38941087380941</v>
+        <v>11.72807617832284</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72">
-        <v>14.27417818758756</v>
+        <v>14.31315085737207</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73">
-        <v>9.323437475369127</v>
+        <v>13.15651636153134</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74">
-        <v>8.812144656786829</v>
+        <v>13.60840319915497</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75">
-        <v>9.898975085713868</v>
+        <v>10.92448867308462</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76">
-        <v>9.028215142626408</v>
+        <v>13.16300385136382</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77">
-        <v>12.30628675928099</v>
+        <v>8.284275101764713</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78">
-        <v>14.65600854111062</v>
+        <v>14.47340519024827</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79">
-        <v>14.92915426939192</v>
+        <v>9.500643419500456</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80">
-        <v>10.39886398647979</v>
+        <v>14.75853994161988</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81">
-        <v>13.29506177224263</v>
+        <v>9.623645171091638</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82">
-        <v>9.696013265270297</v>
+        <v>14.34213367478716</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83">
-        <v>12.53484317108846</v>
+        <v>8.311896652235125</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84">
-        <v>9.742683729622506</v>
+        <v>11.54045084390164</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85">
-        <v>11.28874909043457</v>
+        <v>12.05939544574392</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86">
-        <v>12.3165336760038</v>
+        <v>13.14120706916353</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87">
-        <v>13.28793332270002</v>
+        <v>8.355336333449788</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88">
-        <v>9.283268266378677</v>
+        <v>9.52060514522131</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89">
-        <v>9.917718301625701</v>
+        <v>8.085290516352645</v>
       </c>
     </row>
     <row r="90" spans="1:1">
       <c r="A90">
-        <v>10.70358665943414</v>
+        <v>8.574871134115323</v>
       </c>
     </row>
     <row r="91" spans="1:1">
       <c r="A91">
-        <v>12.91270185018699</v>
+        <v>9.810689972021112</v>
       </c>
     </row>
     <row r="92" spans="1:1">
       <c r="A92">
-        <v>14.86355769520079</v>
+        <v>11.81114800453741</v>
       </c>
     </row>
     <row r="93" spans="1:1">
       <c r="A93">
-        <v>10.12271686040044</v>
+        <v>10.52589627380618</v>
       </c>
     </row>
     <row r="94" spans="1:1">
       <c r="A94">
-        <v>13.85049310189092</v>
+        <v>10.68795269111257</v>
       </c>
     </row>
     <row r="95" spans="1:1">
       <c r="A95">
-        <v>13.56669021208592</v>
+        <v>10.76674860704767</v>
       </c>
     </row>
     <row r="96" spans="1:1">
       <c r="A96">
-        <v>10.92844882736538</v>
+        <v>9.109485150862842</v>
       </c>
     </row>
     <row r="97" spans="1:1">
       <c r="A97">
-        <v>8.417467315451864</v>
+        <v>12.77450243414478</v>
       </c>
     </row>
     <row r="98" spans="1:1">
       <c r="A98">
-        <v>10.6276119350898</v>
+        <v>12.10311584971001</v>
       </c>
     </row>
     <row r="99" spans="1:1">
       <c r="A99">
-        <v>13.47510602916661</v>
+        <v>13.56632499104432</v>
       </c>
     </row>
     <row r="100" spans="1:1">
       <c r="A100">
-        <v>12.46886544557196</v>
+        <v>10.90895878696258</v>
       </c>
     </row>
     <row r="101" spans="1:1">
       <c r="A101">
-        <v>10.87706038295048</v>
+        <v>11.74108674508635</v>
       </c>
     </row>
   </sheetData>
